--- a/DXLibProject_Start/Data/CSV/CollisionData.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF68CF39-8DD2-426B-AC2E-EE7FF987FB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83051133-3F22-47FC-BCCB-6AB47F3BF14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4410" yWindow="-14250" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DXLibProject_Start/Data/CSV/CollisionData.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionData.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83051133-3F22-47FC-BCCB-6AB47F3BF14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C531E5C3-8DFD-48DB-9B74-0075ACAF9B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="-14250" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="-15420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -66,13 +68,72 @@
   </si>
   <si>
     <t>Param[2]</t>
+  </si>
+  <si>
+    <t>Invalid</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>Null</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionTypeName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドラゴンと壁の当たり判定</t>
+    <rPh sb="5" eb="6">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーと壁の当たり判定</t>
+    <rPh sb="6" eb="7">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RangeType</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +143,21 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
@@ -108,8 +184,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -131,7 +211,7 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="CollisionParam"/>
+      <sheetName val="Sheet1"/>
       <sheetName val="Reference"/>
     </sheetNames>
     <sheetDataSet>
@@ -169,8 +249,8 @@
           <cell r="D2">
             <v>80</v>
           </cell>
-          <cell r="E2">
-            <v>-1</v>
+          <cell r="E2" t="str">
+            <v>0.0,0.0,0.0</v>
           </cell>
           <cell r="F2">
             <v>-1</v>
@@ -190,7 +270,7 @@
             <v>0.0,98.0,0.0</v>
           </cell>
           <cell r="E3" t="str">
-            <v xml:space="preserve"> 78.0,195.0,78.0</v>
+            <v xml:space="preserve"> 178.0,195.0,78.0</v>
           </cell>
           <cell r="F3">
             <v>-1</v>
@@ -214,6 +294,90 @@
           </cell>
           <cell r="F4">
             <v>-1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Reference"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>ID</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>RangeType</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>comment</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Param[0]</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Param[1]</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>0</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>Sphere</v>
+          </cell>
+          <cell r="D2">
+            <v>80</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>0.0,0.0,0.0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>1</v>
+          </cell>
+          <cell r="B3">
+            <v>1</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>AABB</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>0.0,98.0,0.0</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v xml:space="preserve"> 78.0,195.0,78.0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>10</v>
+          </cell>
+          <cell r="B4">
+            <v>1</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>AABB</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>0,0,0</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>300.0,300.0,300.0</v>
           </cell>
         </row>
       </sheetData>
@@ -486,14 +650,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,35 +671,89 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="B2">
-        <v>1</v>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2" t="str">
-        <f>VLOOKUP(C2,[1]CollisionParam!$A:$F,4,FALSE)</f>
+      <c r="D2">
+        <f>VLOOKUP(C2,[1]Sheet1!$A:$F,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <f>VLOOKUP(F2,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="str">
+        <f>VLOOKUP(C2,[1]Sheet1!$A:$F,4,FALSE)</f>
         <v>0.0,98.0,0.0</v>
       </c>
-      <c r="F2" t="str">
-        <f>VLOOKUP(C2,[1]CollisionParam!$A:$F,5,FALSE)</f>
+      <c r="H2" t="str">
+        <f>VLOOKUP(C2,[2]Sheet1!$A:$E,5,FALSE)</f>
         <v xml:space="preserve"> 78.0,195.0,78.0</v>
       </c>
-      <c r="G2">
-        <f>VLOOKUP(C2,[1]CollisionParam!$A:$F,6,FALSE)</f>
+      <c r="I2">
+        <f>VLOOKUP(C2,[1]Sheet1!$A:$F,6,FALSE)</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <f>VLOOKUP(C3,[1]Sheet1!$A:$F,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(F3,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="str">
+        <f>VLOOKUP(C3,[1]Sheet1!$A:$F,4,FALSE)</f>
+        <v>0,0,0</v>
+      </c>
+      <c r="H3" t="str">
+        <f>VLOOKUP(C3,[2]Sheet1!$A:$E,5,FALSE)</f>
+        <v>300.0,300.0,300.0</v>
+      </c>
+      <c r="I3">
+        <f>VLOOKUP(C3,[1]Sheet1!$A:$F,6,FALSE)</f>
         <v>-1</v>
       </c>
     </row>
@@ -540,5 +761,102 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C2DF3D82-B2B9-4E3D-AC94-A00962FD53D9}">
+          <x14:formula1>
+            <xm:f>reference!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F3</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0845378D-FB2E-4432-9E50-1B005DFDE695}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="D10" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>